--- a/vch1101/files/kahoot/VCH1101_Kahoot_Unit5_textbook.xlsx
+++ b/vch1101/files/kahoot/VCH1101_Kahoot_Unit5_textbook.xlsx
@@ -707,31 +707,31 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>課本注意事項：電郵嘅「副本抄送」收件人，角色係咩？</t>
+          <t>課本格式表「收件者」一欄要填寫嘅係咩？</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>負責回覆</t>
+          <t>發文者嘅電郵地址</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>需要代為執行工作</t>
+          <t>郵件嘅標題</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>只需知悉，無需執行</t>
+          <t>受文者嘅電郵地址</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>負責審批</t>
+          <t>附件嘅檔案名稱</t>
         </is>
       </c>
       <c r="G9" s="22" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
@@ -746,35 +746,35 @@
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>課本注意事項：幾時要在「附件」一欄標注文件名稱？</t>
+          <t>課本格式表話「收件者」係重要信息。如果寫錯受文者資料，會有咩後果？</t>
         </is>
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>有副本收件人時</t>
+          <t>無法達到溝通目的</t>
         </is>
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>每次發電郵都要</t>
+          <t>郵件會自動被系統刪除</t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t>正文提及附上文件時</t>
+          <t>附件會自動遺失</t>
         </is>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>只有寄給上司時</t>
+          <t>系統會自動轉寄畀其他人</t>
         </is>
       </c>
       <c r="G10" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H10" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" s="1" t="n"/>
@@ -785,35 +785,35 @@
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>課本內容大綱：「上款」又叫咩？</t>
+          <t>課本格式表「發件者」一欄要填嘅係咩？</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>稱謂</t>
+          <t>受文者嘅電郵地址</t>
         </is>
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>標題</t>
+          <t>發文者嘅電郵地址</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
         <is>
-          <t>署名</t>
+          <t>收件者嘅姓名同職銜</t>
         </is>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>自稱</t>
+          <t>郵件嘅主旨</t>
         </is>
       </c>
       <c r="G11" s="25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H11" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" s="1" t="n"/>
@@ -824,35 +824,35 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>課本內容大綱：「下款」包括邊兩部分？</t>
+          <t>課本格式表：「主旨」即郵件嘅咩？課本對佢有咩要求？</t>
         </is>
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>稱謂、主旨</t>
+          <t>郵件嘅第一句；要詳細交代事情</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>引言、結尾</t>
+          <t>附件嘅名稱；要列齊所有文件</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
         <is>
-          <t>自稱、署名</t>
+          <t>發件者嘅姓名職銜；要用全名</t>
         </is>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>日期、時間</t>
+          <t>郵件嘅標題；要簡明扼要，概括郵件核心內容</t>
         </is>
       </c>
       <c r="G12" s="25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H12" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" s="1" t="n"/>
@@ -863,35 +863,35 @@
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>課本內容大綱：正文嘅「主體」要寫咩？</t>
+          <t>課本格式表「副本抄送」一欄要輸入嘅係咩？</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>只寫自我介紹</t>
+          <t>發文者自己嘅電郵地址</t>
         </is>
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t>需要對方跟進的具體事宜，以及提醒對方需注意的事項</t>
+          <t>密件副本嘅受文人電郵地址</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
         <is>
-          <t>只寫聯絡方法</t>
+          <t>接收副本嘅受文人電郵地址</t>
         </is>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>只寫附件清單</t>
+          <t>郵件嘅主旨</t>
         </is>
       </c>
       <c r="G13" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H13" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -902,35 +902,35 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>課本內容大綱：正文嘅「引言」要寫咩？</t>
+          <t>課本格式表「密件副本」一欄要輸入嘅係咩？</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>自我介紹及交代寫作目的</t>
+          <t>接收副本嘅受文人電郵地址</t>
         </is>
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>附上聯絡方法</t>
+          <t>接收密件副本嘅受文人電郵地址</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
         <is>
-          <t>列出附件</t>
+          <t>發文者嘅電郵地址</t>
         </is>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>填寫職銜</t>
+          <t>郵件嘅主旨</t>
         </is>
       </c>
       <c r="G14" s="25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H14" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" s="1" t="n"/>
@@ -941,31 +941,31 @@
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>課本活動二：呢封電郵嘅發文者係邊個？</t>
+          <t>課本注意事項：收到「副本」嘅受文人，需要做咩？</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>非凡科技公司行政助理張浩然</t>
+          <t>只需知悉，無需執行工作</t>
         </is>
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>方總監</t>
+          <t>負責回覆同跟進</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
-          <t>吳女士</t>
+          <t>代為執行相關工作</t>
         </is>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>副經理何文傑</t>
+          <t>負責審批文件</t>
         </is>
       </c>
       <c r="G15" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
@@ -980,35 +980,35 @@
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>課本活動二：呢封電郵嘅受文者（收件者）係邊個？</t>
+          <t>課本格式表話「附件」即郵件夾附嘅文件。課本話幾時要在「附件」一欄標注文件名稱？</t>
         </is>
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
-          <t>副經理何文傑</t>
+          <t>每次發電郵都一定要標注</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>吳女士</t>
+          <t>只有寄件給上司時</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
-          <t>生產部主管</t>
+          <t>有抄送副本嘅時候</t>
         </is>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>方總監</t>
+          <t>正文提及附上文件時</t>
         </is>
       </c>
       <c r="G16" s="25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H16" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" s="1" t="n"/>
@@ -1019,31 +1019,31 @@
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>課本活動二：呢封電郵要抄送副本畀邊個？</t>
+          <t>課本內容大綱：電郵「上款」即稱謂；咁「下款」包括邊兩部分？</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>廣州專上學院</t>
+          <t>稱謂同主旨</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>吳女士</t>
+          <t>引言同結尾</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>方總監（mfong@tech.com.hk）</t>
+          <t>自稱同署名</t>
         </is>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>何副經理</t>
+          <t>日期同時間</t>
         </is>
       </c>
       <c r="G17" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H17" s="26" t="inlineStr">
         <is>
@@ -1058,35 +1058,35 @@
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>課本資料：方總監點解要調整本週工作安排？</t>
+          <t>課本內容大綱：正文嘅「引言」要寫咩？</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>要出差內地工廠</t>
+          <t>需要對方跟進嘅具體事宜</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>要接待家人</t>
+          <t>自我介紹及交代寫作目的</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
         <is>
-          <t>要請病假</t>
+          <t>聯絡方法供查詢之用</t>
         </is>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>要前往澳門出席會議</t>
+          <t>附件嘅名稱同數量</t>
         </is>
       </c>
       <c r="G18" s="25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H18" s="26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" s="1" t="n"/>
@@ -1097,31 +1097,31 @@
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>課本資料二：方總監11月12日（星期二）原定嘅工作係咩？</t>
+          <t>課本內容大綱：正文嘅「主體」要寫咩？</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>上午接待參觀團</t>
+          <t>只寫自我介紹同職銜</t>
         </is>
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>上午與供應商簽約</t>
+          <t>只寫聯絡方法</t>
         </is>
       </c>
       <c r="E19" s="25" t="inlineStr">
         <is>
-          <t>下午出席生產部例會</t>
+          <t>只列出附件名稱</t>
         </is>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>下午主持研發部會議</t>
+          <t>需要對方跟進嘅具體事宜，以及提醒對方需注意嘅事項</t>
         </is>
       </c>
       <c r="G19" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H19" s="26" t="inlineStr">
         <is>
@@ -1136,35 +1136,35 @@
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>課本示範文章：11月12日嘅研發部會議點解要改時間？</t>
+          <t>課本內容大綱：正文嘅「結尾」要寫咩？</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
         <is>
-          <t>方總監提早回港</t>
+          <t>附上聯絡方法（姓名、電話號碼）供查詢之用</t>
         </is>
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>8樓會議室正在維修</t>
+          <t>重複一次主旨嘅內容</t>
         </is>
       </c>
       <c r="E20" s="25" t="inlineStr">
         <is>
-          <t>供應商臨時改期</t>
+          <t>再次填寫收件者嘅電郵地址</t>
         </is>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>何副經理當日下午需出席生產部例會</t>
+          <t>列出所有副本收件人</t>
         </is>
       </c>
       <c r="G20" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H20" s="26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I20" s="1" t="n"/>
@@ -1175,35 +1175,35 @@
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>課本參考答案：研發部會議改到幾點？</t>
+          <t>課本情景：「你是非凡科技公司的行政助理張浩然。」呢封電郵嘅發文者（寫信人）係邊個？</t>
         </is>
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>上午九點到十一點</t>
+          <t>方總監</t>
         </is>
       </c>
       <c r="D21" s="25" t="inlineStr">
         <is>
-          <t>下午兩點到四點</t>
+          <t>副經理何文傑</t>
         </is>
       </c>
       <c r="E21" s="25" t="inlineStr">
         <is>
-          <t>上午十點到十二點</t>
+          <t>行政助理張浩然</t>
         </is>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>下午四點到六點</t>
+          <t>參觀團聯絡人吳女士</t>
         </is>
       </c>
       <c r="G21" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H21" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I21" s="1" t="n"/>
@@ -1214,35 +1214,35 @@
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>課本示範文章：開會地點點解要更改？</t>
+          <t>課本任務：題目要求你撰寫一封簡短電郵畀邊個？</t>
         </is>
       </c>
       <c r="C22" s="25" t="inlineStr">
         <is>
-          <t>8樓會議室已被預訂</t>
+          <t>方總監</t>
         </is>
       </c>
       <c r="D22" s="25" t="inlineStr">
         <is>
-          <t>7樓會議室較大</t>
+          <t>副經理何文傑</t>
         </is>
       </c>
       <c r="E22" s="25" t="inlineStr">
         <is>
-          <t>8樓會議室正進行工程維修</t>
+          <t>參觀團聯絡人吳女士</t>
         </is>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>副經理喜歡7樓</t>
+          <t>生產部主管</t>
         </is>
       </c>
       <c r="G22" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H22" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I22" s="1" t="n"/>
@@ -1253,31 +1253,31 @@
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>課本參考答案：研發部會議最後喺邊個會議室舉行？</t>
+          <t>課本任務：呢封電郵除咗發畀何副經理，仲要抄送副本畀邊個？</t>
         </is>
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
-          <t>8樓會客室</t>
+          <t>參觀團聯絡人吳女士</t>
         </is>
       </c>
       <c r="D23" s="25" t="inlineStr">
         <is>
-          <t>3樓會議室</t>
+          <t>廣州專上學院</t>
         </is>
       </c>
       <c r="E23" s="25" t="inlineStr">
         <is>
-          <t>8樓會議室</t>
+          <t>生產部全體同事</t>
         </is>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>7樓會議室</t>
+          <t>方總監</t>
         </is>
       </c>
       <c r="G23" s="25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
@@ -1292,35 +1292,35 @@
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>課本資料二：研發部會議嘅主題係咩？</t>
+          <t>課本資料一對話：方總監點解要請何副經理代為跟進工作？</t>
         </is>
       </c>
       <c r="C24" s="25" t="inlineStr">
         <is>
-          <t>討論員工加薪</t>
+          <t>他臨時要去澳門參加為期兩天嘅會議</t>
         </is>
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
-          <t>洽談供應商合約</t>
+          <t>他要留在公司與供應商簽約</t>
         </is>
       </c>
       <c r="E24" s="25" t="inlineStr">
         <is>
-          <t>檢討安全生產</t>
+          <t>他要請病假休息</t>
         </is>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>討論新產品的測評結果</t>
+          <t>他要親自接待參觀團</t>
         </is>
       </c>
       <c r="G24" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H24" s="26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I24" s="1" t="n"/>
@@ -1331,35 +1331,35 @@
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>課本資料三：12/11（二）上午 11:00-12:00，7樓會議室嘅狀態係？</t>
+          <t>課本資料二：12/11（二）下午方總監原定嘅工作係咩？</t>
         </is>
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>已預訂</t>
+          <t>上午與供應商簽約（8:30-9:30）</t>
         </is>
       </c>
       <c r="D25" s="25" t="inlineStr">
         <is>
-          <t>可預訂</t>
+          <t>接待參觀團（10:00-12:00）</t>
         </is>
       </c>
       <c r="E25" s="25" t="inlineStr">
         <is>
-          <t>電腦系統更新</t>
+          <t>主持研發部會議（14:00-16:00，8樓會議室）</t>
         </is>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>維修中</t>
+          <t>前往澳門出席會議</t>
         </is>
       </c>
       <c r="G25" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I25" s="1" t="n"/>
@@ -1370,35 +1370,35 @@
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>課本資料二：11月13日（星期三）上午要接待邊個團體？</t>
+          <t>課本資料二：13/11（三）上午方總監原定接待邊個團體？</t>
         </is>
       </c>
       <c r="C26" s="25" t="inlineStr">
         <is>
+          <t>澳門科技大學代表團</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>廣州專上學院資訊科技系師生代表團</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>深圳職業學院師生代表團</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
           <t>北京大學訪問團</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
-        <is>
-          <t>澳門科技大學代表團</t>
-        </is>
-      </c>
-      <c r="E26" s="25" t="inlineStr">
-        <is>
-          <t>深圳職業學院師生代表團</t>
-        </is>
-      </c>
-      <c r="F26" s="25" t="inlineStr">
-        <is>
-          <t>廣州專上學院資訊科技系師生代表團</t>
-        </is>
-      </c>
       <c r="G26" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H26" s="26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I26" s="1" t="n"/>
@@ -1409,35 +1409,35 @@
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>課本參考答案：參觀團嘅聯絡人同電話係？</t>
+          <t>課本示範文章：12/11 嘅研發部會議點解要由下午改到上午？</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>方總監，電話2123-4567</t>
+          <t>方總監提早返港</t>
         </is>
       </c>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>何副經理，電話2852 4781</t>
+          <t>8樓會議室下午要維修</t>
         </is>
       </c>
       <c r="E27" s="25" t="inlineStr">
         <is>
-          <t>吳女士，電話6238 2277</t>
+          <t>供應商臨時改期</t>
         </is>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>李主任，電話68227459</t>
+          <t>何副經理當日下午需出席生產部例會</t>
         </is>
       </c>
       <c r="G27" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H27" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I27" s="1" t="n"/>
@@ -1453,30 +1453,30 @@
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
-          <t>記得帶文件</t>
+          <t>待方總監回公司後匯報相關工作嘅進展</t>
         </is>
       </c>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>提早半小時到場</t>
+          <t>提早半小時到達會場</t>
         </is>
       </c>
       <c r="E28" s="25" t="inlineStr">
         <is>
-          <t>回覆供應商</t>
+          <t>記得帶齊所有文件</t>
         </is>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>待方總監回公司後匯報相關工作的進展</t>
+          <t>代為回覆供應商</t>
         </is>
       </c>
       <c r="G28" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H28" s="26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I28" s="1" t="n"/>
@@ -1487,35 +1487,35 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>課本註明：以上要點必須用文字段落表達；如果以列點方式表達、沒有完整句子，評級不得高於？</t>
+          <t>課本註明：以上要點必須用文字段落表達。如以列點方式表達、沒有完整句子，評級不得高於？</t>
         </is>
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
+          <t>B級</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>D級</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
-        <is>
-          <t>B級</t>
-        </is>
-      </c>
-      <c r="E29" s="27" t="inlineStr">
-        <is>
-          <t>D級</t>
-        </is>
-      </c>
       <c r="F29" s="27" t="inlineStr">
         <is>
           <t>不評級</t>
         </is>
       </c>
       <c r="G29" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H29" s="28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I29" s="1" t="n"/>
